--- a/p_Marker_CATE_EC1.13.11.2_K07104_K00446/primers_cdh_cate1_Supplementary.xlsx
+++ b/p_Marker_CATE_EC1.13.11.2_K07104_K00446/primers_cdh_cate1_Supplementary.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unipiit-my.sharepoint.com/personal/g_semeraro1_studenti_unipi_it/Documents/UniPi/Tesi/PRIMERS/tesiR/5_1.13.11.2_K07104_catE/primers_cmelk07104/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unipiit-my.sharepoint.com/personal/g_semeraro1_studenti_unipi_it/Documents/UniPi/Tesi/THESIS/p_marker_CATE_EC1.13.11.2_K07104_K00446/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="11_AD4D5CB4E552A5DACE1C6445E8DA5B2E5ADEDD88" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{450FBA48-167A-4AE4-9ED0-F1280B762014}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="11_AD4D5CB4E552A5DACE1C6445E8DA5B2E5ADEDD88" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{70B5ED3D-ED74-4742-B313-358DEDB1D394}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="55">
   <si>
     <t>Primer Name</t>
   </si>
@@ -175,9 +175,6 @@
   </si>
   <si>
     <t>uniprot_all</t>
-  </si>
-  <si>
-    <t>PRIMER CMEL</t>
   </si>
   <si>
     <t>origin</t>
@@ -199,7 +196,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -209,6 +206,13 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -234,11 +238,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -519,14 +522,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA6"/>
+  <dimension ref="A2:AA6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="9" max="9" width="9.33203125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
-        <v>50</v>
-      </c>
-    </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>0</v>
@@ -565,10 +566,10 @@
         <v>11</v>
       </c>
       <c r="M2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O2" t="s">
         <v>32</v>
@@ -610,252 +611,252 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3">
         <v>33</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3">
         <v>25</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3">
         <v>2</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" t="s">
         <v>19</v>
       </c>
-      <c r="L3" s="2">
+      <c r="L3">
         <v>60</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="M3" t="s">
         <v>49</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="N3" t="s">
+        <v>51</v>
+      </c>
+      <c r="O3" t="s">
+        <v>45</v>
+      </c>
+      <c r="P3" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q3">
+        <v>25</v>
+      </c>
+      <c r="R3" t="s">
+        <v>15</v>
+      </c>
+      <c r="S3">
+        <v>16</v>
+      </c>
+      <c r="T3">
+        <v>3</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>50</v>
+      </c>
+      <c r="W3" t="s">
+        <v>47</v>
+      </c>
+      <c r="X3">
+        <v>5</v>
+      </c>
+      <c r="Y3" s="1">
+        <v>4.9999999999999998E-8</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4">
+        <v>33</v>
+      </c>
+      <c r="F4">
+        <v>25</v>
+      </c>
+      <c r="G4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4">
+        <v>4</v>
+      </c>
+      <c r="I4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K4" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4">
+        <v>66</v>
+      </c>
+      <c r="M4" t="s">
+        <v>49</v>
+      </c>
+      <c r="N4" t="s">
         <v>52</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="O4" t="s">
         <v>45</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="P4" t="s">
         <v>46</v>
       </c>
-      <c r="Q3" s="2">
+      <c r="Q4">
+        <v>26</v>
+      </c>
+      <c r="R4" t="s">
+        <v>15</v>
+      </c>
+      <c r="S4">
+        <v>16</v>
+      </c>
+      <c r="T4">
+        <v>3</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>50</v>
+      </c>
+      <c r="W4" t="s">
+        <v>47</v>
+      </c>
+      <c r="X4">
+        <v>5</v>
+      </c>
+      <c r="Y4" s="1">
+        <v>4.9999999999999998E-8</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
         <v>25</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" t="s">
         <v>15</v>
       </c>
-      <c r="S3" s="2">
+      <c r="E5">
+        <v>34</v>
+      </c>
+      <c r="F5">
+        <v>25</v>
+      </c>
+      <c r="G5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5">
         <v>16</v>
       </c>
-      <c r="T3" s="2">
+      <c r="I5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J5" t="s">
+        <v>30</v>
+      </c>
+      <c r="K5" t="s">
+        <v>31</v>
+      </c>
+      <c r="L5">
+        <v>60</v>
+      </c>
+      <c r="M5" t="s">
+        <v>49</v>
+      </c>
+      <c r="N5" t="s">
+        <v>53</v>
+      </c>
+      <c r="O5" t="s">
+        <v>45</v>
+      </c>
+      <c r="P5" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q5">
+        <v>27</v>
+      </c>
+      <c r="R5" t="s">
+        <v>15</v>
+      </c>
+      <c r="S5">
+        <v>16</v>
+      </c>
+      <c r="T5">
         <v>3</v>
       </c>
-      <c r="U3" s="2">
+      <c r="U5">
         <v>0</v>
       </c>
-      <c r="V3" s="2">
-        <v>50</v>
-      </c>
-      <c r="W3" s="2" t="s">
+      <c r="V5">
+        <v>60</v>
+      </c>
+      <c r="W5" t="s">
         <v>47</v>
       </c>
-      <c r="X3" s="2">
+      <c r="X5">
         <v>5</v>
       </c>
-      <c r="Y3" s="3">
+      <c r="Y5" s="1">
         <v>4.9999999999999998E-8</v>
       </c>
-      <c r="Z3" s="2" t="s">
+      <c r="Z5" t="s">
         <v>48</v>
       </c>
-      <c r="AA3" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="2">
-        <v>33</v>
-      </c>
-      <c r="F4" s="2">
-        <v>25</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H4" s="2">
-        <v>4</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L4" s="2">
-        <v>66</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="P4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q4" s="2">
-        <v>26</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="S4" s="2">
-        <v>16</v>
-      </c>
-      <c r="T4" s="2">
-        <v>3</v>
-      </c>
-      <c r="U4" s="2">
-        <v>0</v>
-      </c>
-      <c r="V4" s="2">
-        <v>50</v>
-      </c>
-      <c r="W4" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="X4" s="2">
-        <v>5</v>
-      </c>
-      <c r="Y4" s="3">
-        <v>4.9999999999999998E-8</v>
-      </c>
-      <c r="Z4" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AA4" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="2">
-        <v>34</v>
-      </c>
-      <c r="F5" s="2">
-        <v>25</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H5" s="2">
-        <v>16</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="L5" s="2">
-        <v>60</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q5" s="2">
-        <v>27</v>
-      </c>
-      <c r="R5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="S5" s="2">
-        <v>16</v>
-      </c>
-      <c r="T5" s="2">
-        <v>3</v>
-      </c>
-      <c r="U5" s="2">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2">
-        <v>60</v>
-      </c>
-      <c r="W5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="X5" s="2">
-        <v>5</v>
-      </c>
-      <c r="Y5" s="3">
-        <v>4.9999999999999998E-8</v>
-      </c>
-      <c r="Z5" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AA5" s="2" t="s">
+      <c r="AA5" t="s">
         <v>48</v>
       </c>
     </row>
